--- a/out/Petra Speech Logs 2025-05 May_log.xlsx
+++ b/out/Petra Speech Logs 2025-05 May_log.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>05/27/2025</t>
+          <t>05/20/2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -544,6 +544,18 @@
         </is>
       </c>
       <c r="B9" t="inlineStr">
+        <is>
+          <t>05/29/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>05/27/2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>05/29/2025</t>
         </is>
